--- a/ressources/Utilisation de l'IA.xlsx
+++ b/ressources/Utilisation de l'IA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\EnseignementSuperieur\ressources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BF5164-60D1-42DC-B89D-38987312C2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095FDDD7-FD95-4BF2-B850-983520721989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="3156" windowWidth="17280" windowHeight="8880" xr2:uid="{506BB260-50D6-43A4-8C82-FE1DE1D172AF}"/>
+    <workbookView xWindow="3600" yWindow="2100" windowWidth="21600" windowHeight="11295" xr2:uid="{506BB260-50D6-43A4-8C82-FE1DE1D172AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>Membre de l'équipe</t>
   </si>
@@ -141,6 +138,33 @@
   </si>
   <si>
     <t>&lt;input type="hidden" name="id_prof" value="&lt;?php echo $_GET['id_prof']; ?&gt;"&gt;</t>
+  </si>
+  <si>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t>Correction de requêtes vers la BDD</t>
+  </si>
+  <si>
+    <t>Problème de requête mais sans comprendre pourquoi</t>
+  </si>
+  <si>
+    <t>Oubli de nom de table au début de la requête</t>
+  </si>
+  <si>
+    <t>Solution utilisée</t>
+  </si>
+  <si>
+    <t>Savoir comment faire le bouton  bleu ou blanc</t>
+  </si>
+  <si>
+    <t>Je n'ai pas trouvé de réponse sur internet donc j'ai voulu savoir si ça serait compliqué à faire</t>
+  </si>
+  <si>
+    <t>Explication + code</t>
+  </si>
+  <si>
+    <t>Pas utilisé car utilisation de JS</t>
   </si>
 </sst>
 </file>
@@ -518,30 +542,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EB04210-D582-4AE3-B7BF-D5F89EFDEBD0}">
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" customWidth="1"/>
-    <col min="3" max="3" width="34.6640625" customWidth="1"/>
-    <col min="4" max="4" width="69.44140625" customWidth="1"/>
-    <col min="6" max="6" width="99.6640625" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" customWidth="1"/>
-    <col min="8" max="8" width="65.109375" customWidth="1"/>
-    <col min="9" max="9" width="65.88671875" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="38.28515625" customWidth="1"/>
+    <col min="4" max="4" width="83.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="99.7109375" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" customWidth="1"/>
+    <col min="8" max="8" width="65.140625" customWidth="1"/>
+    <col min="9" max="9" width="65.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:9" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:9" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:9" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="2:9" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="2:9" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="2:9" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="2:9" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="2:9" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="2:9" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="2:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="2:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="2:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>0</v>
       </c>
@@ -567,7 +591,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>6</v>
       </c>
@@ -593,7 +617,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>6</v>
       </c>
@@ -619,7 +643,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>6</v>
       </c>
@@ -645,7 +669,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>6</v>
       </c>
@@ -669,6 +693,46 @@
       </c>
       <c r="I15" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/ressources/Utilisation de l'IA.xlsx
+++ b/ressources/Utilisation de l'IA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\EnseignementSuperieur\ressources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095FDDD7-FD95-4BF2-B850-983520721989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38ED410-E349-4000-93EC-146EE661F652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3600" yWindow="2100" windowWidth="21600" windowHeight="11295" xr2:uid="{506BB260-50D6-43A4-8C82-FE1DE1D172AF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{506BB260-50D6-43A4-8C82-FE1DE1D172AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
   <si>
     <t>Membre de l'équipe</t>
   </si>
@@ -95,9 +95,6 @@
     <t>Recherche pour stocker dans le navigateur les données du filtre et id de la page</t>
   </si>
   <si>
-    <t>Solution utiliser</t>
-  </si>
-  <si>
     <t>Choix de la solution sans JS</t>
   </si>
   <si>
@@ -165,13 +162,204 @@
   </si>
   <si>
     <t>Pas utilisé car utilisation de JS</t>
+  </si>
+  <si>
+    <t>Hugo</t>
+  </si>
+  <si>
+    <t>Récupération des éléments de la BDD en PHP</t>
+  </si>
+  <si>
+    <t>Recherche pour afficher des éléments de la BDD sur le site</t>
+  </si>
+  <si>
+    <t>sprint 5</t>
+  </si>
+  <si>
+    <t>Démonstration + Exemples d'utilisations</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00E8C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>$requete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD5CED9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFEE5D43"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD5CED9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00E8C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>$con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFEE5D43"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFE66D"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>prepare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD5CED9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF96E072"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC74DED"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF96E072"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> id </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC74DED"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF96E072"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> course </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC74DED"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF96E072"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> module_id </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFEE5D43"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF96E072"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> :id"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD5CED9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>Crée une modale uniquement en CSS</t>
+  </si>
+  <si>
+    <t>Bug lors de la réutilisation d'une modale JS</t>
+  </si>
+  <si>
+    <t>Exemple de modale en CSS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,6 +372,42 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD5CED9"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00E8C6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFEE5D43"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFE66D"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF96E072"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC74DED"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -206,8 +430,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -542,16 +769,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EB04210-D582-4AE3-B7BF-D5F89EFDEBD0}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="19.28515625" customWidth="1"/>
-    <col min="3" max="3" width="38.28515625" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" customWidth="1"/>
     <col min="4" max="4" width="83.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="99.7109375" customWidth="1"/>
     <col min="7" max="7" width="25.140625" customWidth="1"/>
-    <col min="8" max="8" width="65.140625" customWidth="1"/>
+    <col min="8" max="8" width="89.42578125" customWidth="1"/>
     <col min="9" max="9" width="65.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -588,7 +815,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
@@ -605,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
@@ -631,16 +858,16 @@
         <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
@@ -657,16 +884,16 @@
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="H14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
@@ -683,60 +910,104 @@
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="H15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
         <v>34</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>35</v>
-      </c>
-      <c r="D16" t="s">
-        <v>36</v>
       </c>
       <c r="E16" t="s">
         <v>13</v>
       </c>
       <c r="F16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" t="s">
         <v>37</v>
       </c>
-      <c r="G16" t="s">
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>39</v>
-      </c>
-      <c r="D17" t="s">
-        <v>40</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
       </c>
       <c r="F17" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" t="s">
         <v>41</v>
       </c>
-      <c r="G17" t="s">
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
         <v>42</v>
+      </c>
+      <c r="C18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ressources/Utilisation de l'IA.xlsx
+++ b/ressources/Utilisation de l'IA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\EnseignementSuperieur\ressources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38ED410-E349-4000-93EC-146EE661F652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77332C13-55F3-41B2-AD27-04E18A0CB8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{506BB260-50D6-43A4-8C82-FE1DE1D172AF}"/>
+    <workbookView xWindow="7065" yWindow="2850" windowWidth="21600" windowHeight="11295" xr2:uid="{506BB260-50D6-43A4-8C82-FE1DE1D172AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="60">
   <si>
     <t>Membre de l'équipe</t>
   </si>
@@ -353,6 +353,33 @@
   </si>
   <si>
     <t>Exemple de modale en CSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elena </t>
+  </si>
+  <si>
+    <t>Cahier de recettes</t>
+  </si>
+  <si>
+    <t>On a fourni les fichiers GitHub et la BDD pour que l'IA nous crée notre cahier de recettes</t>
+  </si>
+  <si>
+    <t>Faire les comptes rendus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fourni le GitHub et les sprints </t>
+  </si>
+  <si>
+    <t>Réalisation du cahier des recettes</t>
+  </si>
+  <si>
+    <t>Fait un brouillon des comptes rendus</t>
+  </si>
+  <si>
+    <t>Utilisé</t>
+  </si>
+  <si>
+    <t>Prise comme brouillon puis réecriture</t>
   </si>
 </sst>
 </file>
@@ -769,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EB04210-D582-4AE3-B7BF-D5F89EFDEBD0}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" hidden="1" customWidth="1"/>
@@ -777,7 +804,7 @@
     <col min="3" max="3" width="51.28515625" customWidth="1"/>
     <col min="4" max="4" width="83.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="99.7109375" customWidth="1"/>
-    <col min="7" max="7" width="25.140625" customWidth="1"/>
+    <col min="7" max="7" width="35" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="89.42578125" customWidth="1"/>
     <col min="9" max="9" width="65.85546875" customWidth="1"/>
   </cols>
@@ -1005,6 +1032,40 @@
         <v>37</v>
       </c>
     </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
